--- a/nriss-patch-1/ig/StructureDefinition-mesures-observation-cholesterol-hdl.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-mesures-observation-cholesterol-hdl.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:05:55+00:00</t>
+    <t>2026-10-07T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -646,6 +646,10 @@
     <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
   </si>
   <si>
@@ -661,10 +665,6 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>Observation.extension:mes-original-data</t>
@@ -1713,7 +1713,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>Reference range qualifier</t>
+    <t>Le type de référence permet d'indiquer s'il s'agit d'un intervalle de réfence ou d'un objectif cible.</t>
   </si>
   <si>
     <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -4419,7 +4419,7 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>122</v>
@@ -4445,13 +4445,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
@@ -4473,13 +4473,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4539,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -4659,7 +4659,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
@@ -10009,7 +10009,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10127,7 +10127,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
